--- a/new original/_Lang_Chinese/Lang/CN/Game/Block.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Block.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.282</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Block.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Block.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="572">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
@@ -1286,6 +1286,24 @@
     <t xml:space="preserve">石のフェンス</t>
   </si>
   <si>
+    <t xml:space="preserve">205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cloud block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雲のブロック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alien block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エイリアンのブロック</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alpha 11.1</t>
   </si>
   <si>
@@ -1388,6 +1406,12 @@
     <t xml:space="preserve">EA 23.238</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.286</t>
+  </si>
+  <si>
     <t xml:space="preserve">土方块</t>
   </si>
   <si>
@@ -1695,6 +1719,12 @@
   </si>
   <si>
     <t xml:space="preserve">石头栅栏</t>
+  </si>
+  <si>
+    <t xml:space="preserve">云朵方块</t>
+  </si>
+  <si>
+    <t xml:space="preserve">异形方块</t>
   </si>
   <si>
     <t xml:space="preserve">建筑中不可缺少的立足点。</t>
@@ -1806,7 +1836,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -1818,10 +1848,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C4" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1837,10 +1867,10 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C5" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -1856,10 +1886,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C6" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -1875,10 +1905,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C7" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -1894,10 +1924,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C8" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
@@ -1913,10 +1943,10 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C9" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -1932,10 +1962,10 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C10" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -1951,10 +1981,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C11" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -1970,10 +2000,10 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C12" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
@@ -1989,10 +2019,10 @@
         <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C13" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
@@ -2008,10 +2038,10 @@
         <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C14" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
@@ -2027,10 +2057,10 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C15" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="D15" t="s">
         <v>44</v>
@@ -2046,10 +2076,10 @@
         <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C16" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="D16" t="s">
         <v>47</v>
@@ -2058,7 +2088,7 @@
         <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="G16"/>
       <c r="H16" t="s">
@@ -2070,10 +2100,10 @@
         <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C17" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="D17" t="s">
         <v>44</v>
@@ -2089,10 +2119,10 @@
         <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C18" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="D18" t="s">
         <v>52</v>
@@ -2108,10 +2138,10 @@
         <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C19" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D19" t="s">
         <v>35</v>
@@ -2127,10 +2157,10 @@
         <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C20" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="D20" t="s">
         <v>56</v>
@@ -2146,10 +2176,10 @@
         <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C21" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="D21" t="s">
         <v>59</v>
@@ -2165,10 +2195,10 @@
         <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C22" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D22" t="s">
         <v>35</v>
@@ -2184,10 +2214,10 @@
         <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C23" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D23" t="s">
         <v>35</v>
@@ -2203,10 +2233,10 @@
         <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C24" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D24" t="s">
         <v>35</v>
@@ -2222,10 +2252,10 @@
         <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C25" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="D25" t="s">
         <v>65</v>
@@ -2241,10 +2271,10 @@
         <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C26" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="D26" t="s">
         <v>52</v>
@@ -2260,10 +2290,10 @@
         <v>68</v>
       </c>
       <c r="B27" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C27" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="D27" t="s">
         <v>69</v>
@@ -2279,10 +2309,10 @@
         <v>71</v>
       </c>
       <c r="B28" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C28" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="D28" t="s">
         <v>72</v>
@@ -2298,10 +2328,10 @@
         <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C29" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="D29" t="s">
         <v>75</v>
@@ -2317,10 +2347,10 @@
         <v>77</v>
       </c>
       <c r="B30" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C30" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
@@ -2336,10 +2366,10 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C31" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="D31" t="s">
         <v>47</v>
@@ -2348,7 +2378,7 @@
         <v>48</v>
       </c>
       <c r="F31" t="s">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="G31"/>
       <c r="H31" t="s">
@@ -2360,10 +2390,10 @@
         <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C32" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="D32" t="s">
         <v>80</v>
@@ -2379,10 +2409,10 @@
         <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C33" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D33" t="s">
         <v>83</v>
@@ -2398,10 +2428,10 @@
         <v>85</v>
       </c>
       <c r="B34" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C34" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D34" t="s">
         <v>83</v>
@@ -2417,10 +2447,10 @@
         <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C35" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="D35" t="s">
         <v>83</v>
@@ -2436,10 +2466,10 @@
         <v>87</v>
       </c>
       <c r="B36" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C36" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="D36" t="s">
         <v>88</v>
@@ -2455,10 +2485,10 @@
         <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C37" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="D37" t="s">
         <v>91</v>
@@ -2474,10 +2504,10 @@
         <v>93</v>
       </c>
       <c r="B38" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C38" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="D38" t="s">
         <v>94</v>
@@ -2493,10 +2523,10 @@
         <v>96</v>
       </c>
       <c r="B39" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C39" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="D39" t="s">
         <v>97</v>
@@ -2512,10 +2542,10 @@
         <v>99</v>
       </c>
       <c r="B40" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C40" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D40" t="s">
         <v>29</v>
@@ -2531,10 +2561,10 @@
         <v>100</v>
       </c>
       <c r="B41" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C41" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D41" t="s">
         <v>29</v>
@@ -2550,10 +2580,10 @@
         <v>101</v>
       </c>
       <c r="B42" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C42" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D42" t="s">
         <v>29</v>
@@ -2569,10 +2599,10 @@
         <v>102</v>
       </c>
       <c r="B43" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C43" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D43" t="s">
         <v>29</v>
@@ -2588,10 +2618,10 @@
         <v>103</v>
       </c>
       <c r="B44" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C44" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D44" t="s">
         <v>29</v>
@@ -2607,10 +2637,10 @@
         <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C45" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
@@ -2626,10 +2656,10 @@
         <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C46" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="D46" t="s">
         <v>75</v>
@@ -2645,10 +2675,10 @@
         <v>106</v>
       </c>
       <c r="B47" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C47" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="D47" t="s">
         <v>14</v>
@@ -2664,10 +2694,10 @@
         <v>107</v>
       </c>
       <c r="B48" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C48" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="D48" t="s">
         <v>108</v>
@@ -2683,10 +2713,10 @@
         <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C49" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="D49" t="s">
         <v>111</v>
@@ -2702,10 +2732,10 @@
         <v>113</v>
       </c>
       <c r="B50" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C50" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D50" t="s">
         <v>114</v>
@@ -2721,10 +2751,10 @@
         <v>116</v>
       </c>
       <c r="B51" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C51" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="D51" t="s">
         <v>117</v>
@@ -2740,10 +2770,10 @@
         <v>119</v>
       </c>
       <c r="B52" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C52" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="D52" t="s">
         <v>120</v>
@@ -2759,10 +2789,10 @@
         <v>122</v>
       </c>
       <c r="B53" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C53" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="D53" t="s">
         <v>123</v>
@@ -2778,10 +2808,10 @@
         <v>125</v>
       </c>
       <c r="B54" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C54" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="D54" t="s">
         <v>126</v>
@@ -2797,10 +2827,10 @@
         <v>128</v>
       </c>
       <c r="B55" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C55" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="D55" t="s">
         <v>129</v>
@@ -2816,10 +2846,10 @@
         <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C56" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="D56" t="s">
         <v>132</v>
@@ -2835,10 +2865,10 @@
         <v>134</v>
       </c>
       <c r="B57" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C57" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="D57" t="s">
         <v>135</v>
@@ -2854,10 +2884,10 @@
         <v>137</v>
       </c>
       <c r="B58" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C58" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="D58" t="s">
         <v>117</v>
@@ -2873,10 +2903,10 @@
         <v>138</v>
       </c>
       <c r="B59" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C59" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="D59" t="s">
         <v>139</v>
@@ -2892,10 +2922,10 @@
         <v>141</v>
       </c>
       <c r="B60" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C60" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="D60" t="s">
         <v>142</v>
@@ -2911,10 +2941,10 @@
         <v>144</v>
       </c>
       <c r="B61" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C61" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="D61" t="s">
         <v>142</v>
@@ -2930,10 +2960,10 @@
         <v>145</v>
       </c>
       <c r="B62" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C62" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="D62" t="s">
         <v>142</v>
@@ -2949,10 +2979,10 @@
         <v>146</v>
       </c>
       <c r="B63" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C63" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="D63" t="s">
         <v>147</v>
@@ -2968,10 +2998,10 @@
         <v>149</v>
       </c>
       <c r="B64" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C64" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D64" t="s">
         <v>150</v>
@@ -2987,10 +3017,10 @@
         <v>152</v>
       </c>
       <c r="B65" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C65" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D65" t="s">
         <v>150</v>
@@ -3006,10 +3036,10 @@
         <v>153</v>
       </c>
       <c r="B66" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C66" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D66" t="s">
         <v>150</v>
@@ -3025,10 +3055,10 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C67" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="D67" t="s">
         <v>120</v>
@@ -3044,10 +3074,10 @@
         <v>155</v>
       </c>
       <c r="B68" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C68" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="D68" t="s">
         <v>14</v>
@@ -3063,10 +3093,10 @@
         <v>156</v>
       </c>
       <c r="B69" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C69" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="D69" t="s">
         <v>14</v>
@@ -3082,10 +3112,10 @@
         <v>157</v>
       </c>
       <c r="B70" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C70" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="D70" t="s">
         <v>158</v>
@@ -3101,10 +3131,10 @@
         <v>160</v>
       </c>
       <c r="B71" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C71" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="D71" t="s">
         <v>161</v>
@@ -3120,10 +3150,10 @@
         <v>163</v>
       </c>
       <c r="B72" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C72" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="D72" t="s">
         <v>158</v>
@@ -3139,10 +3169,10 @@
         <v>164</v>
       </c>
       <c r="B73" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C73" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="D73" t="s">
         <v>165</v>
@@ -3158,10 +3188,10 @@
         <v>167</v>
       </c>
       <c r="B74" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C74" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="D74" t="s">
         <v>168</v>
@@ -3177,10 +3207,10 @@
         <v>170</v>
       </c>
       <c r="B75" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C75" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="D75" t="s">
         <v>168</v>
@@ -3196,10 +3226,10 @@
         <v>171</v>
       </c>
       <c r="B76" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C76" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="D76" t="s">
         <v>158</v>
@@ -3215,10 +3245,10 @@
         <v>172</v>
       </c>
       <c r="B77" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C77" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="D77" t="s">
         <v>168</v>
@@ -3234,10 +3264,10 @@
         <v>173</v>
       </c>
       <c r="B78" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C78" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="D78" t="s">
         <v>158</v>
@@ -3253,10 +3283,10 @@
         <v>174</v>
       </c>
       <c r="B79" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C79" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="D79" t="s">
         <v>168</v>
@@ -3272,10 +3302,10 @@
         <v>175</v>
       </c>
       <c r="B80" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C80" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="D80" t="s">
         <v>176</v>
@@ -3291,10 +3321,10 @@
         <v>178</v>
       </c>
       <c r="B81" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C81" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="D81" t="s">
         <v>176</v>
@@ -3310,10 +3340,10 @@
         <v>179</v>
       </c>
       <c r="B82" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C82" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="D82" t="s">
         <v>176</v>
@@ -3329,10 +3359,10 @@
         <v>180</v>
       </c>
       <c r="B83" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C83" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="D83" t="s">
         <v>158</v>
@@ -3348,10 +3378,10 @@
         <v>181</v>
       </c>
       <c r="B84" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C84" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="D84" t="s">
         <v>168</v>
@@ -3367,10 +3397,10 @@
         <v>182</v>
       </c>
       <c r="B85" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C85" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="D85" t="s">
         <v>168</v>
@@ -3386,10 +3416,10 @@
         <v>183</v>
       </c>
       <c r="B86" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C86" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="D86" t="s">
         <v>184</v>
@@ -3405,10 +3435,10 @@
         <v>186</v>
       </c>
       <c r="B87" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C87" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="D87" t="s">
         <v>187</v>
@@ -3424,10 +3454,10 @@
         <v>189</v>
       </c>
       <c r="B88" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C88" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="D88" t="s">
         <v>187</v>
@@ -3443,10 +3473,10 @@
         <v>190</v>
       </c>
       <c r="B89" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C89" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="D89" t="s">
         <v>187</v>
@@ -3462,10 +3492,10 @@
         <v>191</v>
       </c>
       <c r="B90" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C90" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="D90" t="s">
         <v>161</v>
@@ -3481,10 +3511,10 @@
         <v>192</v>
       </c>
       <c r="B91" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C91" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="D91" t="s">
         <v>193</v>
@@ -3500,10 +3530,10 @@
         <v>195</v>
       </c>
       <c r="B92" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C92" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D92" t="s">
         <v>114</v>
@@ -3519,10 +3549,10 @@
         <v>196</v>
       </c>
       <c r="B93" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C93" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D93" t="s">
         <v>114</v>
@@ -3538,10 +3568,10 @@
         <v>197</v>
       </c>
       <c r="B94" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C94" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="D94" t="s">
         <v>198</v>
@@ -3557,10 +3587,10 @@
         <v>200</v>
       </c>
       <c r="B95" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C95" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="D95" t="s">
         <v>139</v>
@@ -3576,10 +3606,10 @@
         <v>201</v>
       </c>
       <c r="B96" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C96" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="D96" t="s">
         <v>202</v>
@@ -3595,10 +3625,10 @@
         <v>204</v>
       </c>
       <c r="B97" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C97" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="D97" t="s">
         <v>202</v>
@@ -3614,10 +3644,10 @@
         <v>205</v>
       </c>
       <c r="B98" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C98" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="D98" t="s">
         <v>206</v>
@@ -3633,10 +3663,10 @@
         <v>208</v>
       </c>
       <c r="B99" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C99" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="D99" t="s">
         <v>209</v>
@@ -3652,10 +3682,10 @@
         <v>211</v>
       </c>
       <c r="B100" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C100" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="D100" t="s">
         <v>212</v>
@@ -3671,10 +3701,10 @@
         <v>214</v>
       </c>
       <c r="B101" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C101" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="D101" t="s">
         <v>215</v>
@@ -3690,10 +3720,10 @@
         <v>217</v>
       </c>
       <c r="B102" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C102" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="D102" t="s">
         <v>218</v>
@@ -3709,10 +3739,10 @@
         <v>220</v>
       </c>
       <c r="B103" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C103" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="D103" t="s">
         <v>221</v>
@@ -3728,10 +3758,10 @@
         <v>223</v>
       </c>
       <c r="B104" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C104" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="D104" t="s">
         <v>221</v>
@@ -3747,10 +3777,10 @@
         <v>224</v>
       </c>
       <c r="B105" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C105" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="D105" t="s">
         <v>225</v>
@@ -3766,10 +3796,10 @@
         <v>227</v>
       </c>
       <c r="B106" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C106" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="D106" t="s">
         <v>225</v>
@@ -3785,10 +3815,10 @@
         <v>228</v>
       </c>
       <c r="B107" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C107" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="D107" t="s">
         <v>225</v>
@@ -3804,10 +3834,10 @@
         <v>229</v>
       </c>
       <c r="B108" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C108" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="D108" t="s">
         <v>225</v>
@@ -3823,10 +3853,10 @@
         <v>230</v>
       </c>
       <c r="B109" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C109" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="D109" t="s">
         <v>20</v>
@@ -3842,10 +3872,10 @@
         <v>231</v>
       </c>
       <c r="B110" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C110" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="D110" t="s">
         <v>232</v>
@@ -3861,10 +3891,10 @@
         <v>234</v>
       </c>
       <c r="B111" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C111" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D111" t="s">
         <v>235</v>
@@ -3880,10 +3910,10 @@
         <v>237</v>
       </c>
       <c r="B112" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C112" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D112" t="s">
         <v>235</v>
@@ -3899,10 +3929,10 @@
         <v>238</v>
       </c>
       <c r="B113" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C113" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D113" t="s">
         <v>235</v>
@@ -3918,10 +3948,10 @@
         <v>239</v>
       </c>
       <c r="B114" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C114" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D114" t="s">
         <v>235</v>
@@ -3937,10 +3967,10 @@
         <v>240</v>
       </c>
       <c r="B115" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C115" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="D115" t="s">
         <v>241</v>
@@ -3956,10 +3986,10 @@
         <v>243</v>
       </c>
       <c r="B116" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C116" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="D116" t="s">
         <v>241</v>
@@ -3975,10 +4005,10 @@
         <v>244</v>
       </c>
       <c r="B117" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C117" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="D117" t="s">
         <v>245</v>
@@ -3994,10 +4024,10 @@
         <v>247</v>
       </c>
       <c r="B118" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C118" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="D118" t="s">
         <v>248</v>
@@ -4013,10 +4043,10 @@
         <v>250</v>
       </c>
       <c r="B119" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C119" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="D119" t="s">
         <v>248</v>
@@ -4032,10 +4062,10 @@
         <v>251</v>
       </c>
       <c r="B120" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C120" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="D120" t="s">
         <v>248</v>
@@ -4051,10 +4081,10 @@
         <v>252</v>
       </c>
       <c r="B121" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C121" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D121" t="s">
         <v>253</v>
@@ -4070,10 +4100,10 @@
         <v>255</v>
       </c>
       <c r="B122" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C122" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D122" t="s">
         <v>253</v>
@@ -4089,10 +4119,10 @@
         <v>256</v>
       </c>
       <c r="B123" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C123" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D123" t="s">
         <v>257</v>
@@ -4108,10 +4138,10 @@
         <v>259</v>
       </c>
       <c r="B124" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C124" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D124" t="s">
         <v>257</v>
@@ -4127,10 +4157,10 @@
         <v>260</v>
       </c>
       <c r="B125" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C125" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D125" t="s">
         <v>257</v>
@@ -4146,10 +4176,10 @@
         <v>261</v>
       </c>
       <c r="B126" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C126" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="D126" t="s">
         <v>248</v>
@@ -4165,10 +4195,10 @@
         <v>262</v>
       </c>
       <c r="B127" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C127" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D127" t="s">
         <v>263</v>
@@ -4184,10 +4214,10 @@
         <v>265</v>
       </c>
       <c r="B128" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C128" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="D128" t="s">
         <v>158</v>
@@ -4203,10 +4233,10 @@
         <v>266</v>
       </c>
       <c r="B129" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C129" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D129" t="s">
         <v>29</v>
@@ -4222,10 +4252,10 @@
         <v>267</v>
       </c>
       <c r="B130" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C130" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="D130" t="s">
         <v>120</v>
@@ -4241,10 +4271,10 @@
         <v>268</v>
       </c>
       <c r="B131" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C131" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D131" t="s">
         <v>269</v>
@@ -4253,7 +4283,7 @@
         <v>270</v>
       </c>
       <c r="F131" t="s">
-        <v>561</v>
+        <v>571</v>
       </c>
       <c r="G131" t="s">
         <v>271</v>
@@ -4267,10 +4297,10 @@
         <v>273</v>
       </c>
       <c r="B132" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C132" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D132" t="s">
         <v>35</v>
@@ -4286,10 +4316,10 @@
         <v>274</v>
       </c>
       <c r="B133" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C133" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="D133" t="s">
         <v>275</v>
@@ -4305,10 +4335,10 @@
         <v>277</v>
       </c>
       <c r="B134" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C134" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="D134" t="s">
         <v>278</v>
@@ -4324,10 +4354,10 @@
         <v>280</v>
       </c>
       <c r="B135" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C135" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="D135" t="s">
         <v>281</v>
@@ -4343,10 +4373,10 @@
         <v>283</v>
       </c>
       <c r="B136" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C136" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="D136" t="s">
         <v>281</v>
@@ -4362,10 +4392,10 @@
         <v>285</v>
       </c>
       <c r="B137" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C137" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="D137" t="s">
         <v>281</v>
@@ -4381,10 +4411,10 @@
         <v>287</v>
       </c>
       <c r="B138" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C138" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="D138" t="s">
         <v>221</v>
@@ -4400,10 +4430,10 @@
         <v>288</v>
       </c>
       <c r="B139" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C139" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="D139" t="s">
         <v>289</v>
@@ -4419,10 +4449,10 @@
         <v>291</v>
       </c>
       <c r="B140" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C140" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="D140" t="s">
         <v>120</v>
@@ -4438,10 +4468,10 @@
         <v>292</v>
       </c>
       <c r="B141" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C141" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="D141" t="s">
         <v>123</v>
@@ -4457,10 +4487,10 @@
         <v>293</v>
       </c>
       <c r="B142" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C142" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="D142" t="s">
         <v>117</v>
@@ -4476,10 +4506,10 @@
         <v>294</v>
       </c>
       <c r="B143" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C143" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D143" t="s">
         <v>35</v>
@@ -4495,10 +4525,10 @@
         <v>295</v>
       </c>
       <c r="B144" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C144" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="D144" t="s">
         <v>38</v>
@@ -4514,10 +4544,10 @@
         <v>296</v>
       </c>
       <c r="B145" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C145" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="D145" t="s">
         <v>117</v>
@@ -4533,10 +4563,10 @@
         <v>297</v>
       </c>
       <c r="B146" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C146" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D146" t="s">
         <v>35</v>
@@ -4552,10 +4582,10 @@
         <v>298</v>
       </c>
       <c r="B147" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C147" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D147" t="s">
         <v>299</v>
@@ -4571,10 +4601,10 @@
         <v>301</v>
       </c>
       <c r="B148" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C148" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="D148" t="s">
         <v>302</v>
@@ -4590,10 +4620,10 @@
         <v>304</v>
       </c>
       <c r="B149" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C149" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="D149" t="s">
         <v>302</v>
@@ -4609,10 +4639,10 @@
         <v>305</v>
       </c>
       <c r="B150" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C150" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="D150" t="s">
         <v>306</v>
@@ -4628,10 +4658,10 @@
         <v>308</v>
       </c>
       <c r="B151" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C151" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D151" t="s">
         <v>150</v>
@@ -4647,10 +4677,10 @@
         <v>309</v>
       </c>
       <c r="B152" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C152" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="D152" t="s">
         <v>310</v>
@@ -4666,10 +4696,10 @@
         <v>312</v>
       </c>
       <c r="B153" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C153" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="D153" t="s">
         <v>313</v>
@@ -4685,10 +4715,10 @@
         <v>315</v>
       </c>
       <c r="B154" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C154" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="D154" t="s">
         <v>316</v>
@@ -4704,10 +4734,10 @@
         <v>318</v>
       </c>
       <c r="B155" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C155" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="D155" t="s">
         <v>316</v>
@@ -4723,10 +4753,10 @@
         <v>319</v>
       </c>
       <c r="B156" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C156" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="D156" t="s">
         <v>75</v>
@@ -4742,10 +4772,10 @@
         <v>320</v>
       </c>
       <c r="B157" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C157" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="D157" t="s">
         <v>111</v>
@@ -4761,10 +4791,10 @@
         <v>321</v>
       </c>
       <c r="B158" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C158" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="D158" t="s">
         <v>221</v>
@@ -4780,10 +4810,10 @@
         <v>322</v>
       </c>
       <c r="B159" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C159" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D159" t="s">
         <v>150</v>
@@ -4799,10 +4829,10 @@
         <v>323</v>
       </c>
       <c r="B160" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C160" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D160" t="s">
         <v>150</v>
@@ -4818,10 +4848,10 @@
         <v>324</v>
       </c>
       <c r="B161" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C161" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D161" t="s">
         <v>150</v>
@@ -4837,10 +4867,10 @@
         <v>325</v>
       </c>
       <c r="B162" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C162" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="D162" t="s">
         <v>108</v>
@@ -4856,10 +4886,10 @@
         <v>326</v>
       </c>
       <c r="B163" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C163" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D163" t="s">
         <v>327</v>
@@ -4875,10 +4905,10 @@
         <v>329</v>
       </c>
       <c r="B164" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C164" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="D164" t="s">
         <v>289</v>
@@ -4894,10 +4924,10 @@
         <v>330</v>
       </c>
       <c r="B165" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C165" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="D165" t="s">
         <v>331</v>
@@ -4913,7 +4943,7 @@
         <v>333</v>
       </c>
       <c r="B166" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C166" t="s">
         <v>335</v>
@@ -4932,7 +4962,7 @@
         <v>336</v>
       </c>
       <c r="B167" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C167" t="s">
         <v>335</v>
@@ -4951,10 +4981,10 @@
         <v>337</v>
       </c>
       <c r="B168" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C168" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D168" t="s">
         <v>338</v>
@@ -4970,10 +5000,10 @@
         <v>340</v>
       </c>
       <c r="B169" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C169" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="D169" t="s">
         <v>341</v>
@@ -4989,10 +5019,10 @@
         <v>343</v>
       </c>
       <c r="B170" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C170" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="D170" t="s">
         <v>344</v>
@@ -5008,10 +5038,10 @@
         <v>346</v>
       </c>
       <c r="B171" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C171" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="D171" t="s">
         <v>347</v>
@@ -5027,10 +5057,10 @@
         <v>349</v>
       </c>
       <c r="B172" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C172" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="D172" t="s">
         <v>139</v>
@@ -5046,10 +5076,10 @@
         <v>350</v>
       </c>
       <c r="B173" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C173" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="D173" t="s">
         <v>139</v>
@@ -5065,10 +5095,10 @@
         <v>351</v>
       </c>
       <c r="B174" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C174" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="D174" t="s">
         <v>352</v>
@@ -5084,10 +5114,10 @@
         <v>354</v>
       </c>
       <c r="B175" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C175" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="D175" t="s">
         <v>355</v>
@@ -5103,10 +5133,10 @@
         <v>357</v>
       </c>
       <c r="B176" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C176" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="D176" t="s">
         <v>355</v>
@@ -5122,10 +5152,10 @@
         <v>358</v>
       </c>
       <c r="B177" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C177" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="D177" t="s">
         <v>359</v>
@@ -5141,10 +5171,10 @@
         <v>361</v>
       </c>
       <c r="B178" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C178" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D178" t="s">
         <v>29</v>
@@ -5160,10 +5190,10 @@
         <v>362</v>
       </c>
       <c r="B179" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C179" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D179" t="s">
         <v>29</v>
@@ -5179,10 +5209,10 @@
         <v>363</v>
       </c>
       <c r="B180" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C180" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D180" t="s">
         <v>29</v>
@@ -5198,10 +5228,10 @@
         <v>364</v>
       </c>
       <c r="B181" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C181" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D181" t="s">
         <v>29</v>
@@ -5217,10 +5247,10 @@
         <v>365</v>
       </c>
       <c r="B182" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C182" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D182" t="s">
         <v>29</v>
@@ -5236,10 +5266,10 @@
         <v>366</v>
       </c>
       <c r="B183" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C183" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D183" t="s">
         <v>29</v>
@@ -5255,10 +5285,10 @@
         <v>367</v>
       </c>
       <c r="B184" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C184" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D184" t="s">
         <v>29</v>
@@ -5274,10 +5304,10 @@
         <v>368</v>
       </c>
       <c r="B185" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C185" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D185" t="s">
         <v>29</v>
@@ -5293,10 +5323,10 @@
         <v>369</v>
       </c>
       <c r="B186" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C186" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D186" t="s">
         <v>29</v>
@@ -5312,10 +5342,10 @@
         <v>370</v>
       </c>
       <c r="B187" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C187" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D187" t="s">
         <v>29</v>
@@ -5331,10 +5361,10 @@
         <v>371</v>
       </c>
       <c r="B188" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C188" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="D188" t="s">
         <v>14</v>
@@ -5350,10 +5380,10 @@
         <v>372</v>
       </c>
       <c r="B189" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C189" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="D189" t="s">
         <v>373</v>
@@ -5369,10 +5399,10 @@
         <v>375</v>
       </c>
       <c r="B190" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="C190" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="D190" t="s">
         <v>376</v>
@@ -5388,10 +5418,10 @@
         <v>378</v>
       </c>
       <c r="B191" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C191" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="D191" t="s">
         <v>376</v>
@@ -5407,10 +5437,10 @@
         <v>379</v>
       </c>
       <c r="B192" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C192" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="D192" t="s">
         <v>380</v>
@@ -5426,10 +5456,10 @@
         <v>382</v>
       </c>
       <c r="B193" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C193" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="D193" t="s">
         <v>383</v>
@@ -5445,10 +5475,10 @@
         <v>385</v>
       </c>
       <c r="B194" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="C194" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="D194" t="s">
         <v>386</v>
@@ -5464,10 +5494,10 @@
         <v>388</v>
       </c>
       <c r="B195" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C195" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="D195" t="s">
         <v>389</v>
@@ -5483,10 +5513,10 @@
         <v>391</v>
       </c>
       <c r="B196" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C196" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="D196" t="s">
         <v>392</v>
@@ -5502,10 +5532,10 @@
         <v>394</v>
       </c>
       <c r="B197" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C197" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="D197" t="s">
         <v>395</v>
@@ -5521,10 +5551,10 @@
         <v>397</v>
       </c>
       <c r="B198" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C198" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="D198" t="s">
         <v>398</v>
@@ -5540,10 +5570,10 @@
         <v>400</v>
       </c>
       <c r="B199" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C199" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="D199" t="s">
         <v>401</v>
@@ -5559,10 +5589,10 @@
         <v>403</v>
       </c>
       <c r="B200" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C200" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="D200" t="s">
         <v>404</v>
@@ -5578,10 +5608,10 @@
         <v>406</v>
       </c>
       <c r="B201" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C201" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="D201" t="s">
         <v>407</v>
@@ -5597,10 +5627,10 @@
         <v>409</v>
       </c>
       <c r="B202" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C202" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="D202" t="s">
         <v>410</v>
@@ -5616,10 +5646,10 @@
         <v>412</v>
       </c>
       <c r="B203" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="C203" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="D203" t="s">
         <v>413</v>
@@ -5635,10 +5665,10 @@
         <v>415</v>
       </c>
       <c r="B204" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C204" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="D204" t="s">
         <v>59</v>
@@ -5654,10 +5684,10 @@
         <v>416</v>
       </c>
       <c r="B205" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C205" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="D205" t="s">
         <v>417</v>
@@ -5673,10 +5703,10 @@
         <v>419</v>
       </c>
       <c r="B206" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C206" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="D206" t="s">
         <v>417</v>
@@ -5692,10 +5722,10 @@
         <v>420</v>
       </c>
       <c r="B207" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C207" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="D207" t="s">
         <v>421</v>
@@ -5705,6 +5735,44 @@
       </c>
       <c r="G207"/>
       <c r="H207"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>423</v>
+      </c>
+      <c r="B208" t="s">
+        <v>463</v>
+      </c>
+      <c r="C208" t="s">
+        <v>568</v>
+      </c>
+      <c r="D208" t="s">
+        <v>424</v>
+      </c>
+      <c r="E208" t="s">
+        <v>425</v>
+      </c>
+      <c r="G208"/>
+      <c r="H208"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>426</v>
+      </c>
+      <c r="B209" t="s">
+        <v>464</v>
+      </c>
+      <c r="C209" t="s">
+        <v>569</v>
+      </c>
+      <c r="D209" t="s">
+        <v>427</v>
+      </c>
+      <c r="E209" t="s">
+        <v>428</v>
+      </c>
+      <c r="G209"/>
+      <c r="H209"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Block.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Block.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="587">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
@@ -1304,6 +1304,39 @@
     <t xml:space="preserve">エイリアンのブロック</t>
   </si>
   <si>
+    <t xml:space="preserve">207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alien wall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エイリアンの壁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alien pillar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エイリアンの柱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alpha 11.1</t>
   </si>
   <si>
@@ -1412,6 +1445,12 @@
     <t xml:space="preserve">EA 23.286</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.289</t>
+  </si>
+  <si>
     <t xml:space="preserve">土方块</t>
   </si>
   <si>
@@ -1725,6 +1764,12 @@
   </si>
   <si>
     <t xml:space="preserve">异形方块</t>
+  </si>
+  <si>
+    <t xml:space="preserve">异形墙壁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">异形柱子</t>
   </si>
   <si>
     <t xml:space="preserve">建筑中不可缺少的立足点。</t>
@@ -1836,7 +1881,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -1848,10 +1893,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C4" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1867,10 +1912,10 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C5" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -1886,10 +1931,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C6" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -1905,10 +1950,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C7" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -1924,10 +1969,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C8" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
@@ -1943,10 +1988,10 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C9" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -1962,10 +2007,10 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C10" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -1981,10 +2026,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C11" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -2000,10 +2045,10 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C12" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
@@ -2019,10 +2064,10 @@
         <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C13" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
@@ -2038,10 +2083,10 @@
         <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C14" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
@@ -2057,10 +2102,10 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C15" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="D15" t="s">
         <v>44</v>
@@ -2076,10 +2121,10 @@
         <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="C16" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="D16" t="s">
         <v>47</v>
@@ -2088,7 +2133,7 @@
         <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="G16"/>
       <c r="H16" t="s">
@@ -2100,10 +2145,10 @@
         <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C17" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="D17" t="s">
         <v>44</v>
@@ -2119,10 +2164,10 @@
         <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C18" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="D18" t="s">
         <v>52</v>
@@ -2138,10 +2183,10 @@
         <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C19" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="D19" t="s">
         <v>35</v>
@@ -2157,10 +2202,10 @@
         <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C20" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="D20" t="s">
         <v>56</v>
@@ -2176,10 +2221,10 @@
         <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C21" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="D21" t="s">
         <v>59</v>
@@ -2195,10 +2240,10 @@
         <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C22" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="D22" t="s">
         <v>35</v>
@@ -2214,10 +2259,10 @@
         <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C23" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="D23" t="s">
         <v>35</v>
@@ -2233,10 +2278,10 @@
         <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C24" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="D24" t="s">
         <v>35</v>
@@ -2252,10 +2297,10 @@
         <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C25" t="s">
-        <v>480</v>
+        <v>493</v>
       </c>
       <c r="D25" t="s">
         <v>65</v>
@@ -2271,10 +2316,10 @@
         <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C26" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="D26" t="s">
         <v>52</v>
@@ -2290,10 +2335,10 @@
         <v>68</v>
       </c>
       <c r="B27" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C27" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="D27" t="s">
         <v>69</v>
@@ -2309,10 +2354,10 @@
         <v>71</v>
       </c>
       <c r="B28" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C28" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="D28" t="s">
         <v>72</v>
@@ -2328,10 +2373,10 @@
         <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C29" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="D29" t="s">
         <v>75</v>
@@ -2347,10 +2392,10 @@
         <v>77</v>
       </c>
       <c r="B30" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C30" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
@@ -2366,10 +2411,10 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="C31" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="D31" t="s">
         <v>47</v>
@@ -2378,7 +2423,7 @@
         <v>48</v>
       </c>
       <c r="F31" t="s">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="G31"/>
       <c r="H31" t="s">
@@ -2390,10 +2435,10 @@
         <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C32" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
       <c r="D32" t="s">
         <v>80</v>
@@ -2409,10 +2454,10 @@
         <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C33" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="D33" t="s">
         <v>83</v>
@@ -2428,10 +2473,10 @@
         <v>85</v>
       </c>
       <c r="B34" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C34" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="D34" t="s">
         <v>83</v>
@@ -2447,10 +2492,10 @@
         <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C35" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="D35" t="s">
         <v>83</v>
@@ -2466,10 +2511,10 @@
         <v>87</v>
       </c>
       <c r="B36" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C36" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="D36" t="s">
         <v>88</v>
@@ -2485,10 +2530,10 @@
         <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C37" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="D37" t="s">
         <v>91</v>
@@ -2504,10 +2549,10 @@
         <v>93</v>
       </c>
       <c r="B38" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C38" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="D38" t="s">
         <v>94</v>
@@ -2523,10 +2568,10 @@
         <v>96</v>
       </c>
       <c r="B39" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C39" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="D39" t="s">
         <v>97</v>
@@ -2542,10 +2587,10 @@
         <v>99</v>
       </c>
       <c r="B40" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C40" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D40" t="s">
         <v>29</v>
@@ -2561,10 +2606,10 @@
         <v>100</v>
       </c>
       <c r="B41" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C41" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D41" t="s">
         <v>29</v>
@@ -2580,10 +2625,10 @@
         <v>101</v>
       </c>
       <c r="B42" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C42" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D42" t="s">
         <v>29</v>
@@ -2599,10 +2644,10 @@
         <v>102</v>
       </c>
       <c r="B43" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C43" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D43" t="s">
         <v>29</v>
@@ -2618,10 +2663,10 @@
         <v>103</v>
       </c>
       <c r="B44" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C44" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D44" t="s">
         <v>29</v>
@@ -2637,10 +2682,10 @@
         <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C45" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
@@ -2656,10 +2701,10 @@
         <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C46" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="D46" t="s">
         <v>75</v>
@@ -2675,10 +2720,10 @@
         <v>106</v>
       </c>
       <c r="B47" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C47" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="D47" t="s">
         <v>14</v>
@@ -2694,10 +2739,10 @@
         <v>107</v>
       </c>
       <c r="B48" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="C48" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="D48" t="s">
         <v>108</v>
@@ -2713,10 +2758,10 @@
         <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C49" t="s">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="D49" t="s">
         <v>111</v>
@@ -2732,10 +2777,10 @@
         <v>113</v>
       </c>
       <c r="B50" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C50" t="s">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="D50" t="s">
         <v>114</v>
@@ -2751,10 +2796,10 @@
         <v>116</v>
       </c>
       <c r="B51" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C51" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="D51" t="s">
         <v>117</v>
@@ -2770,10 +2815,10 @@
         <v>119</v>
       </c>
       <c r="B52" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C52" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="D52" t="s">
         <v>120</v>
@@ -2789,10 +2834,10 @@
         <v>122</v>
       </c>
       <c r="B53" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C53" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="D53" t="s">
         <v>123</v>
@@ -2808,10 +2853,10 @@
         <v>125</v>
       </c>
       <c r="B54" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C54" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="D54" t="s">
         <v>126</v>
@@ -2827,10 +2872,10 @@
         <v>128</v>
       </c>
       <c r="B55" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C55" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="D55" t="s">
         <v>129</v>
@@ -2846,10 +2891,10 @@
         <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C56" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="D56" t="s">
         <v>132</v>
@@ -2865,10 +2910,10 @@
         <v>134</v>
       </c>
       <c r="B57" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C57" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="D57" t="s">
         <v>135</v>
@@ -2884,10 +2929,10 @@
         <v>137</v>
       </c>
       <c r="B58" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C58" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="D58" t="s">
         <v>117</v>
@@ -2903,10 +2948,10 @@
         <v>138</v>
       </c>
       <c r="B59" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C59" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="D59" t="s">
         <v>139</v>
@@ -2922,10 +2967,10 @@
         <v>141</v>
       </c>
       <c r="B60" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C60" t="s">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="D60" t="s">
         <v>142</v>
@@ -2941,10 +2986,10 @@
         <v>144</v>
       </c>
       <c r="B61" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C61" t="s">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="D61" t="s">
         <v>142</v>
@@ -2960,10 +3005,10 @@
         <v>145</v>
       </c>
       <c r="B62" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C62" t="s">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="D62" t="s">
         <v>142</v>
@@ -2979,10 +3024,10 @@
         <v>146</v>
       </c>
       <c r="B63" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C63" t="s">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="D63" t="s">
         <v>147</v>
@@ -2998,10 +3043,10 @@
         <v>149</v>
       </c>
       <c r="B64" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C64" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="D64" t="s">
         <v>150</v>
@@ -3017,10 +3062,10 @@
         <v>152</v>
       </c>
       <c r="B65" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C65" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="D65" t="s">
         <v>150</v>
@@ -3036,10 +3081,10 @@
         <v>153</v>
       </c>
       <c r="B66" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C66" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="D66" t="s">
         <v>150</v>
@@ -3055,10 +3100,10 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C67" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="D67" t="s">
         <v>120</v>
@@ -3074,10 +3119,10 @@
         <v>155</v>
       </c>
       <c r="B68" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C68" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="D68" t="s">
         <v>14</v>
@@ -3093,10 +3138,10 @@
         <v>156</v>
       </c>
       <c r="B69" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C69" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="D69" t="s">
         <v>14</v>
@@ -3112,10 +3157,10 @@
         <v>157</v>
       </c>
       <c r="B70" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C70" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="D70" t="s">
         <v>158</v>
@@ -3131,10 +3176,10 @@
         <v>160</v>
       </c>
       <c r="B71" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C71" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="D71" t="s">
         <v>161</v>
@@ -3150,10 +3195,10 @@
         <v>163</v>
       </c>
       <c r="B72" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C72" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="D72" t="s">
         <v>158</v>
@@ -3169,10 +3214,10 @@
         <v>164</v>
       </c>
       <c r="B73" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C73" t="s">
-        <v>506</v>
+        <v>519</v>
       </c>
       <c r="D73" t="s">
         <v>165</v>
@@ -3188,10 +3233,10 @@
         <v>167</v>
       </c>
       <c r="B74" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C74" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="D74" t="s">
         <v>168</v>
@@ -3207,10 +3252,10 @@
         <v>170</v>
       </c>
       <c r="B75" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C75" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="D75" t="s">
         <v>168</v>
@@ -3226,10 +3271,10 @@
         <v>171</v>
       </c>
       <c r="B76" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C76" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="D76" t="s">
         <v>158</v>
@@ -3245,10 +3290,10 @@
         <v>172</v>
       </c>
       <c r="B77" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C77" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="D77" t="s">
         <v>168</v>
@@ -3264,10 +3309,10 @@
         <v>173</v>
       </c>
       <c r="B78" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C78" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="D78" t="s">
         <v>158</v>
@@ -3283,10 +3328,10 @@
         <v>174</v>
       </c>
       <c r="B79" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C79" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="D79" t="s">
         <v>168</v>
@@ -3302,10 +3347,10 @@
         <v>175</v>
       </c>
       <c r="B80" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C80" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="D80" t="s">
         <v>176</v>
@@ -3321,10 +3366,10 @@
         <v>178</v>
       </c>
       <c r="B81" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C81" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="D81" t="s">
         <v>176</v>
@@ -3340,10 +3385,10 @@
         <v>179</v>
       </c>
       <c r="B82" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C82" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="D82" t="s">
         <v>176</v>
@@ -3359,10 +3404,10 @@
         <v>180</v>
       </c>
       <c r="B83" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C83" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="D83" t="s">
         <v>158</v>
@@ -3378,10 +3423,10 @@
         <v>181</v>
       </c>
       <c r="B84" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C84" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="D84" t="s">
         <v>168</v>
@@ -3397,10 +3442,10 @@
         <v>182</v>
       </c>
       <c r="B85" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C85" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="D85" t="s">
         <v>168</v>
@@ -3416,10 +3461,10 @@
         <v>183</v>
       </c>
       <c r="B86" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C86" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="D86" t="s">
         <v>184</v>
@@ -3435,10 +3480,10 @@
         <v>186</v>
       </c>
       <c r="B87" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C87" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="D87" t="s">
         <v>187</v>
@@ -3454,10 +3499,10 @@
         <v>189</v>
       </c>
       <c r="B88" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C88" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="D88" t="s">
         <v>187</v>
@@ -3473,10 +3518,10 @@
         <v>190</v>
       </c>
       <c r="B89" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C89" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="D89" t="s">
         <v>187</v>
@@ -3492,10 +3537,10 @@
         <v>191</v>
       </c>
       <c r="B90" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C90" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="D90" t="s">
         <v>161</v>
@@ -3511,10 +3556,10 @@
         <v>192</v>
       </c>
       <c r="B91" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C91" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="D91" t="s">
         <v>193</v>
@@ -3530,10 +3575,10 @@
         <v>195</v>
       </c>
       <c r="B92" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C92" t="s">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="D92" t="s">
         <v>114</v>
@@ -3549,10 +3594,10 @@
         <v>196</v>
       </c>
       <c r="B93" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C93" t="s">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="D93" t="s">
         <v>114</v>
@@ -3568,10 +3613,10 @@
         <v>197</v>
       </c>
       <c r="B94" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C94" t="s">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="D94" t="s">
         <v>198</v>
@@ -3587,10 +3632,10 @@
         <v>200</v>
       </c>
       <c r="B95" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C95" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="D95" t="s">
         <v>139</v>
@@ -3606,10 +3651,10 @@
         <v>201</v>
       </c>
       <c r="B96" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C96" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="D96" t="s">
         <v>202</v>
@@ -3625,10 +3670,10 @@
         <v>204</v>
       </c>
       <c r="B97" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C97" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="D97" t="s">
         <v>202</v>
@@ -3644,10 +3689,10 @@
         <v>205</v>
       </c>
       <c r="B98" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C98" t="s">
-        <v>514</v>
+        <v>527</v>
       </c>
       <c r="D98" t="s">
         <v>206</v>
@@ -3663,10 +3708,10 @@
         <v>208</v>
       </c>
       <c r="B99" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C99" t="s">
-        <v>515</v>
+        <v>528</v>
       </c>
       <c r="D99" t="s">
         <v>209</v>
@@ -3682,10 +3727,10 @@
         <v>211</v>
       </c>
       <c r="B100" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C100" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="D100" t="s">
         <v>212</v>
@@ -3701,10 +3746,10 @@
         <v>214</v>
       </c>
       <c r="B101" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C101" t="s">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c r="D101" t="s">
         <v>215</v>
@@ -3720,10 +3765,10 @@
         <v>217</v>
       </c>
       <c r="B102" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C102" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="D102" t="s">
         <v>218</v>
@@ -3739,10 +3784,10 @@
         <v>220</v>
       </c>
       <c r="B103" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C103" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="D103" t="s">
         <v>221</v>
@@ -3758,10 +3803,10 @@
         <v>223</v>
       </c>
       <c r="B104" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C104" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="D104" t="s">
         <v>221</v>
@@ -3777,10 +3822,10 @@
         <v>224</v>
       </c>
       <c r="B105" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C105" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="D105" t="s">
         <v>225</v>
@@ -3796,10 +3841,10 @@
         <v>227</v>
       </c>
       <c r="B106" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C106" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="D106" t="s">
         <v>225</v>
@@ -3815,10 +3860,10 @@
         <v>228</v>
       </c>
       <c r="B107" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C107" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="D107" t="s">
         <v>225</v>
@@ -3834,10 +3879,10 @@
         <v>229</v>
       </c>
       <c r="B108" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C108" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="D108" t="s">
         <v>225</v>
@@ -3853,10 +3898,10 @@
         <v>230</v>
       </c>
       <c r="B109" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C109" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="D109" t="s">
         <v>20</v>
@@ -3872,10 +3917,10 @@
         <v>231</v>
       </c>
       <c r="B110" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C110" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="D110" t="s">
         <v>232</v>
@@ -3891,10 +3936,10 @@
         <v>234</v>
       </c>
       <c r="B111" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C111" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="D111" t="s">
         <v>235</v>
@@ -3910,10 +3955,10 @@
         <v>237</v>
       </c>
       <c r="B112" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C112" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="D112" t="s">
         <v>235</v>
@@ -3929,10 +3974,10 @@
         <v>238</v>
       </c>
       <c r="B113" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C113" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="D113" t="s">
         <v>235</v>
@@ -3948,10 +3993,10 @@
         <v>239</v>
       </c>
       <c r="B114" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C114" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="D114" t="s">
         <v>235</v>
@@ -3967,10 +4012,10 @@
         <v>240</v>
       </c>
       <c r="B115" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C115" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="D115" t="s">
         <v>241</v>
@@ -3986,10 +4031,10 @@
         <v>243</v>
       </c>
       <c r="B116" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C116" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="D116" t="s">
         <v>241</v>
@@ -4005,10 +4050,10 @@
         <v>244</v>
       </c>
       <c r="B117" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="C117" t="s">
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="D117" t="s">
         <v>245</v>
@@ -4024,10 +4069,10 @@
         <v>247</v>
       </c>
       <c r="B118" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C118" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="D118" t="s">
         <v>248</v>
@@ -4043,10 +4088,10 @@
         <v>250</v>
       </c>
       <c r="B119" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C119" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="D119" t="s">
         <v>248</v>
@@ -4062,10 +4107,10 @@
         <v>251</v>
       </c>
       <c r="B120" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C120" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="D120" t="s">
         <v>248</v>
@@ -4081,10 +4126,10 @@
         <v>252</v>
       </c>
       <c r="B121" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C121" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="D121" t="s">
         <v>253</v>
@@ -4100,10 +4145,10 @@
         <v>255</v>
       </c>
       <c r="B122" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C122" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="D122" t="s">
         <v>253</v>
@@ -4119,10 +4164,10 @@
         <v>256</v>
       </c>
       <c r="B123" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C123" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="D123" t="s">
         <v>257</v>
@@ -4138,10 +4183,10 @@
         <v>259</v>
       </c>
       <c r="B124" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C124" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="D124" t="s">
         <v>257</v>
@@ -4157,10 +4202,10 @@
         <v>260</v>
       </c>
       <c r="B125" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C125" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="D125" t="s">
         <v>257</v>
@@ -4176,10 +4221,10 @@
         <v>261</v>
       </c>
       <c r="B126" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C126" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="D126" t="s">
         <v>248</v>
@@ -4195,10 +4240,10 @@
         <v>262</v>
       </c>
       <c r="B127" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C127" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="D127" t="s">
         <v>263</v>
@@ -4214,10 +4259,10 @@
         <v>265</v>
       </c>
       <c r="B128" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C128" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="D128" t="s">
         <v>158</v>
@@ -4233,10 +4278,10 @@
         <v>266</v>
       </c>
       <c r="B129" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C129" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D129" t="s">
         <v>29</v>
@@ -4252,10 +4297,10 @@
         <v>267</v>
       </c>
       <c r="B130" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C130" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="D130" t="s">
         <v>120</v>
@@ -4271,10 +4316,10 @@
         <v>268</v>
       </c>
       <c r="B131" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="C131" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="D131" t="s">
         <v>269</v>
@@ -4283,7 +4328,7 @@
         <v>270</v>
       </c>
       <c r="F131" t="s">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="G131" t="s">
         <v>271</v>
@@ -4297,10 +4342,10 @@
         <v>273</v>
       </c>
       <c r="B132" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C132" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="D132" t="s">
         <v>35</v>
@@ -4316,10 +4361,10 @@
         <v>274</v>
       </c>
       <c r="B133" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C133" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
       <c r="D133" t="s">
         <v>275</v>
@@ -4335,10 +4380,10 @@
         <v>277</v>
       </c>
       <c r="B134" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C134" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="D134" t="s">
         <v>278</v>
@@ -4354,10 +4399,10 @@
         <v>280</v>
       </c>
       <c r="B135" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C135" t="s">
-        <v>532</v>
+        <v>545</v>
       </c>
       <c r="D135" t="s">
         <v>281</v>
@@ -4373,10 +4418,10 @@
         <v>283</v>
       </c>
       <c r="B136" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C136" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="D136" t="s">
         <v>281</v>
@@ -4392,10 +4437,10 @@
         <v>285</v>
       </c>
       <c r="B137" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C137" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="D137" t="s">
         <v>281</v>
@@ -4411,10 +4456,10 @@
         <v>287</v>
       </c>
       <c r="B138" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C138" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="D138" t="s">
         <v>221</v>
@@ -4430,10 +4475,10 @@
         <v>288</v>
       </c>
       <c r="B139" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C139" t="s">
-        <v>535</v>
+        <v>548</v>
       </c>
       <c r="D139" t="s">
         <v>289</v>
@@ -4449,10 +4494,10 @@
         <v>291</v>
       </c>
       <c r="B140" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C140" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="D140" t="s">
         <v>120</v>
@@ -4468,10 +4513,10 @@
         <v>292</v>
       </c>
       <c r="B141" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C141" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="D141" t="s">
         <v>123</v>
@@ -4487,10 +4532,10 @@
         <v>293</v>
       </c>
       <c r="B142" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C142" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="D142" t="s">
         <v>117</v>
@@ -4506,10 +4551,10 @@
         <v>294</v>
       </c>
       <c r="B143" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C143" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="D143" t="s">
         <v>35</v>
@@ -4525,10 +4570,10 @@
         <v>295</v>
       </c>
       <c r="B144" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C144" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="D144" t="s">
         <v>38</v>
@@ -4544,10 +4589,10 @@
         <v>296</v>
       </c>
       <c r="B145" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="C145" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="D145" t="s">
         <v>117</v>
@@ -4563,10 +4608,10 @@
         <v>297</v>
       </c>
       <c r="B146" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="C146" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="D146" t="s">
         <v>35</v>
@@ -4582,10 +4627,10 @@
         <v>298</v>
       </c>
       <c r="B147" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C147" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="D147" t="s">
         <v>299</v>
@@ -4601,10 +4646,10 @@
         <v>301</v>
       </c>
       <c r="B148" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C148" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
       <c r="D148" t="s">
         <v>302</v>
@@ -4620,10 +4665,10 @@
         <v>304</v>
       </c>
       <c r="B149" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C149" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
       <c r="D149" t="s">
         <v>302</v>
@@ -4639,10 +4684,10 @@
         <v>305</v>
       </c>
       <c r="B150" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C150" t="s">
-        <v>538</v>
+        <v>551</v>
       </c>
       <c r="D150" t="s">
         <v>306</v>
@@ -4658,10 +4703,10 @@
         <v>308</v>
       </c>
       <c r="B151" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="C151" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="D151" t="s">
         <v>150</v>
@@ -4677,10 +4722,10 @@
         <v>309</v>
       </c>
       <c r="B152" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="C152" t="s">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="D152" t="s">
         <v>310</v>
@@ -4696,10 +4741,10 @@
         <v>312</v>
       </c>
       <c r="B153" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="C153" t="s">
-        <v>540</v>
+        <v>553</v>
       </c>
       <c r="D153" t="s">
         <v>313</v>
@@ -4715,10 +4760,10 @@
         <v>315</v>
       </c>
       <c r="B154" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="C154" t="s">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="D154" t="s">
         <v>316</v>
@@ -4734,10 +4779,10 @@
         <v>318</v>
       </c>
       <c r="B155" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="C155" t="s">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="D155" t="s">
         <v>316</v>
@@ -4753,10 +4798,10 @@
         <v>319</v>
       </c>
       <c r="B156" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C156" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="D156" t="s">
         <v>75</v>
@@ -4772,10 +4817,10 @@
         <v>320</v>
       </c>
       <c r="B157" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="C157" t="s">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="D157" t="s">
         <v>111</v>
@@ -4791,10 +4836,10 @@
         <v>321</v>
       </c>
       <c r="B158" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C158" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="D158" t="s">
         <v>221</v>
@@ -4810,10 +4855,10 @@
         <v>322</v>
       </c>
       <c r="B159" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="C159" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="D159" t="s">
         <v>150</v>
@@ -4829,10 +4874,10 @@
         <v>323</v>
       </c>
       <c r="B160" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="C160" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="D160" t="s">
         <v>150</v>
@@ -4848,10 +4893,10 @@
         <v>324</v>
       </c>
       <c r="B161" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="C161" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="D161" t="s">
         <v>150</v>
@@ -4867,10 +4912,10 @@
         <v>325</v>
       </c>
       <c r="B162" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="C162" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="D162" t="s">
         <v>108</v>
@@ -4886,10 +4931,10 @@
         <v>326</v>
       </c>
       <c r="B163" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C163" t="s">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="D163" t="s">
         <v>327</v>
@@ -4905,10 +4950,10 @@
         <v>329</v>
       </c>
       <c r="B164" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C164" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="D164" t="s">
         <v>289</v>
@@ -4924,10 +4969,10 @@
         <v>330</v>
       </c>
       <c r="B165" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C165" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="D165" t="s">
         <v>331</v>
@@ -4943,7 +4988,7 @@
         <v>333</v>
       </c>
       <c r="B166" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="C166" t="s">
         <v>335</v>
@@ -4962,7 +5007,7 @@
         <v>336</v>
       </c>
       <c r="B167" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="C167" t="s">
         <v>335</v>
@@ -4981,10 +5026,10 @@
         <v>337</v>
       </c>
       <c r="B168" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C168" t="s">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="D168" t="s">
         <v>338</v>
@@ -5000,10 +5045,10 @@
         <v>340</v>
       </c>
       <c r="B169" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="C169" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="D169" t="s">
         <v>341</v>
@@ -5019,10 +5064,10 @@
         <v>343</v>
       </c>
       <c r="B170" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="C170" t="s">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="D170" t="s">
         <v>344</v>
@@ -5038,10 +5083,10 @@
         <v>346</v>
       </c>
       <c r="B171" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="C171" t="s">
-        <v>548</v>
+        <v>561</v>
       </c>
       <c r="D171" t="s">
         <v>347</v>
@@ -5057,10 +5102,10 @@
         <v>349</v>
       </c>
       <c r="B172" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="C172" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="D172" t="s">
         <v>139</v>
@@ -5076,10 +5121,10 @@
         <v>350</v>
       </c>
       <c r="B173" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="C173" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="D173" t="s">
         <v>139</v>
@@ -5095,10 +5140,10 @@
         <v>351</v>
       </c>
       <c r="B174" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="C174" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="D174" t="s">
         <v>352</v>
@@ -5114,10 +5159,10 @@
         <v>354</v>
       </c>
       <c r="B175" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="C175" t="s">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="D175" t="s">
         <v>355</v>
@@ -5133,10 +5178,10 @@
         <v>357</v>
       </c>
       <c r="B176" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="C176" t="s">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="D176" t="s">
         <v>355</v>
@@ -5152,10 +5197,10 @@
         <v>358</v>
       </c>
       <c r="B177" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="C177" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="D177" t="s">
         <v>359</v>
@@ -5171,10 +5216,10 @@
         <v>361</v>
       </c>
       <c r="B178" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="C178" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D178" t="s">
         <v>29</v>
@@ -5190,10 +5235,10 @@
         <v>362</v>
       </c>
       <c r="B179" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="C179" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D179" t="s">
         <v>29</v>
@@ -5209,10 +5254,10 @@
         <v>363</v>
       </c>
       <c r="B180" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="C180" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D180" t="s">
         <v>29</v>
@@ -5228,10 +5273,10 @@
         <v>364</v>
       </c>
       <c r="B181" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="C181" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D181" t="s">
         <v>29</v>
@@ -5247,10 +5292,10 @@
         <v>365</v>
       </c>
       <c r="B182" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="C182" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D182" t="s">
         <v>29</v>
@@ -5266,10 +5311,10 @@
         <v>366</v>
       </c>
       <c r="B183" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="C183" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D183" t="s">
         <v>29</v>
@@ -5285,10 +5330,10 @@
         <v>367</v>
       </c>
       <c r="B184" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="C184" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D184" t="s">
         <v>29</v>
@@ -5304,10 +5349,10 @@
         <v>368</v>
       </c>
       <c r="B185" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="C185" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D185" t="s">
         <v>29</v>
@@ -5323,10 +5368,10 @@
         <v>369</v>
       </c>
       <c r="B186" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="C186" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D186" t="s">
         <v>29</v>
@@ -5342,10 +5387,10 @@
         <v>370</v>
       </c>
       <c r="B187" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="C187" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="D187" t="s">
         <v>29</v>
@@ -5361,10 +5406,10 @@
         <v>371</v>
       </c>
       <c r="B188" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="C188" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="D188" t="s">
         <v>14</v>
@@ -5380,10 +5425,10 @@
         <v>372</v>
       </c>
       <c r="B189" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="C189" t="s">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="D189" t="s">
         <v>373</v>
@@ -5399,10 +5444,10 @@
         <v>375</v>
       </c>
       <c r="B190" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="C190" t="s">
-        <v>553</v>
+        <v>566</v>
       </c>
       <c r="D190" t="s">
         <v>376</v>
@@ -5418,10 +5463,10 @@
         <v>378</v>
       </c>
       <c r="B191" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="C191" t="s">
-        <v>553</v>
+        <v>566</v>
       </c>
       <c r="D191" t="s">
         <v>376</v>
@@ -5437,10 +5482,10 @@
         <v>379</v>
       </c>
       <c r="B192" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="C192" t="s">
-        <v>554</v>
+        <v>567</v>
       </c>
       <c r="D192" t="s">
         <v>380</v>
@@ -5456,10 +5501,10 @@
         <v>382</v>
       </c>
       <c r="B193" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="C193" t="s">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="D193" t="s">
         <v>383</v>
@@ -5475,10 +5520,10 @@
         <v>385</v>
       </c>
       <c r="B194" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="C194" t="s">
-        <v>556</v>
+        <v>569</v>
       </c>
       <c r="D194" t="s">
         <v>386</v>
@@ -5494,10 +5539,10 @@
         <v>388</v>
       </c>
       <c r="B195" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="C195" t="s">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="D195" t="s">
         <v>389</v>
@@ -5513,10 +5558,10 @@
         <v>391</v>
       </c>
       <c r="B196" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="C196" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="D196" t="s">
         <v>392</v>
@@ -5532,10 +5577,10 @@
         <v>394</v>
       </c>
       <c r="B197" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="C197" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="D197" t="s">
         <v>395</v>
@@ -5551,10 +5596,10 @@
         <v>397</v>
       </c>
       <c r="B198" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="C198" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="D198" t="s">
         <v>398</v>
@@ -5570,10 +5615,10 @@
         <v>400</v>
       </c>
       <c r="B199" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="C199" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="D199" t="s">
         <v>401</v>
@@ -5589,10 +5634,10 @@
         <v>403</v>
       </c>
       <c r="B200" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="C200" t="s">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="D200" t="s">
         <v>404</v>
@@ -5608,10 +5653,10 @@
         <v>406</v>
       </c>
       <c r="B201" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="C201" t="s">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="D201" t="s">
         <v>407</v>
@@ -5627,10 +5672,10 @@
         <v>409</v>
       </c>
       <c r="B202" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="C202" t="s">
-        <v>564</v>
+        <v>577</v>
       </c>
       <c r="D202" t="s">
         <v>410</v>
@@ -5646,10 +5691,10 @@
         <v>412</v>
       </c>
       <c r="B203" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="C203" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="D203" t="s">
         <v>413</v>
@@ -5665,10 +5710,10 @@
         <v>415</v>
       </c>
       <c r="B204" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="C204" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="D204" t="s">
         <v>59</v>
@@ -5684,10 +5729,10 @@
         <v>416</v>
       </c>
       <c r="B205" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="C205" t="s">
-        <v>566</v>
+        <v>579</v>
       </c>
       <c r="D205" t="s">
         <v>417</v>
@@ -5703,10 +5748,10 @@
         <v>419</v>
       </c>
       <c r="B206" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="C206" t="s">
-        <v>566</v>
+        <v>579</v>
       </c>
       <c r="D206" t="s">
         <v>417</v>
@@ -5722,10 +5767,10 @@
         <v>420</v>
       </c>
       <c r="B207" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="C207" t="s">
-        <v>567</v>
+        <v>580</v>
       </c>
       <c r="D207" t="s">
         <v>421</v>
@@ -5741,10 +5786,10 @@
         <v>423</v>
       </c>
       <c r="B208" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="C208" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="D208" t="s">
         <v>424</v>
@@ -5760,10 +5805,10 @@
         <v>426</v>
       </c>
       <c r="B209" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="C209" t="s">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="D209" t="s">
         <v>427</v>
@@ -5773,6 +5818,139 @@
       </c>
       <c r="G209"/>
       <c r="H209"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>429</v>
+      </c>
+      <c r="B210" t="s">
+        <v>476</v>
+      </c>
+      <c r="C210" t="s">
+        <v>582</v>
+      </c>
+      <c r="D210" t="s">
+        <v>427</v>
+      </c>
+      <c r="E210" t="s">
+        <v>428</v>
+      </c>
+      <c r="G210"/>
+      <c r="H210"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>430</v>
+      </c>
+      <c r="B211" t="s">
+        <v>477</v>
+      </c>
+      <c r="C211" t="s">
+        <v>583</v>
+      </c>
+      <c r="D211" t="s">
+        <v>431</v>
+      </c>
+      <c r="E211" t="s">
+        <v>432</v>
+      </c>
+      <c r="G211"/>
+      <c r="H211"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>433</v>
+      </c>
+      <c r="B212" t="s">
+        <v>477</v>
+      </c>
+      <c r="C212" t="s">
+        <v>583</v>
+      </c>
+      <c r="D212" t="s">
+        <v>431</v>
+      </c>
+      <c r="E212" t="s">
+        <v>432</v>
+      </c>
+      <c r="G212"/>
+      <c r="H212"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>434</v>
+      </c>
+      <c r="B213" t="s">
+        <v>477</v>
+      </c>
+      <c r="C213" t="s">
+        <v>583</v>
+      </c>
+      <c r="D213" t="s">
+        <v>431</v>
+      </c>
+      <c r="E213" t="s">
+        <v>432</v>
+      </c>
+      <c r="G213"/>
+      <c r="H213"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>435</v>
+      </c>
+      <c r="B214" t="s">
+        <v>477</v>
+      </c>
+      <c r="C214" t="s">
+        <v>584</v>
+      </c>
+      <c r="D214" t="s">
+        <v>436</v>
+      </c>
+      <c r="E214" t="s">
+        <v>437</v>
+      </c>
+      <c r="G214"/>
+      <c r="H214"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>438</v>
+      </c>
+      <c r="B215" t="s">
+        <v>477</v>
+      </c>
+      <c r="C215" t="s">
+        <v>584</v>
+      </c>
+      <c r="D215" t="s">
+        <v>436</v>
+      </c>
+      <c r="E215" t="s">
+        <v>437</v>
+      </c>
+      <c r="G215"/>
+      <c r="H215"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>439</v>
+      </c>
+      <c r="B216" t="s">
+        <v>477</v>
+      </c>
+      <c r="C216" t="s">
+        <v>584</v>
+      </c>
+      <c r="D216" t="s">
+        <v>436</v>
+      </c>
+      <c r="E216" t="s">
+        <v>437</v>
+      </c>
+      <c r="G216"/>
+      <c r="H216"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Block.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Block.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="572">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
@@ -1304,39 +1304,6 @@
     <t xml:space="preserve">エイリアンのブロック</t>
   </si>
   <si>
-    <t xml:space="preserve">207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">alien wall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エイリアンの壁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">alien pillar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エイリアンの柱</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213</t>
-  </si>
-  <si>
     <t xml:space="preserve">Alpha 11.1</t>
   </si>
   <si>
@@ -1445,12 +1412,6 @@
     <t xml:space="preserve">EA 23.286</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.289</t>
-  </si>
-  <si>
     <t xml:space="preserve">土方块</t>
   </si>
   <si>
@@ -1764,12 +1725,6 @@
   </si>
   <si>
     <t xml:space="preserve">异形方块</t>
-  </si>
-  <si>
-    <t xml:space="preserve">异形墙壁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">异形柱子</t>
   </si>
   <si>
     <t xml:space="preserve">建筑中不可缺少的立足点。</t>
@@ -1881,7 +1836,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -1893,10 +1848,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C4" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1912,10 +1867,10 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C5" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -1931,10 +1886,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C6" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -1950,10 +1905,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C7" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
@@ -1969,10 +1924,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C8" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
@@ -1988,10 +1943,10 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C9" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -2007,10 +1962,10 @@
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C10" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
@@ -2026,10 +1981,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C11" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -2045,10 +2000,10 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C12" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
@@ -2064,10 +2019,10 @@
         <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C13" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
@@ -2083,10 +2038,10 @@
         <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C14" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
@@ -2102,10 +2057,10 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C15" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="D15" t="s">
         <v>44</v>
@@ -2121,10 +2076,10 @@
         <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="C16" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="D16" t="s">
         <v>47</v>
@@ -2133,7 +2088,7 @@
         <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>585</v>
+        <v>570</v>
       </c>
       <c r="G16"/>
       <c r="H16" t="s">
@@ -2145,10 +2100,10 @@
         <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C17" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="D17" t="s">
         <v>44</v>
@@ -2164,10 +2119,10 @@
         <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C18" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="D18" t="s">
         <v>52</v>
@@ -2183,10 +2138,10 @@
         <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C19" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="D19" t="s">
         <v>35</v>
@@ -2202,10 +2157,10 @@
         <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C20" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="D20" t="s">
         <v>56</v>
@@ -2221,10 +2176,10 @@
         <v>58</v>
       </c>
       <c r="B21" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C21" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="D21" t="s">
         <v>59</v>
@@ -2240,10 +2195,10 @@
         <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C22" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="D22" t="s">
         <v>35</v>
@@ -2259,10 +2214,10 @@
         <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C23" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="D23" t="s">
         <v>35</v>
@@ -2278,10 +2233,10 @@
         <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C24" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="D24" t="s">
         <v>35</v>
@@ -2297,10 +2252,10 @@
         <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C25" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="D25" t="s">
         <v>65</v>
@@ -2316,10 +2271,10 @@
         <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C26" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="D26" t="s">
         <v>52</v>
@@ -2335,10 +2290,10 @@
         <v>68</v>
       </c>
       <c r="B27" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C27" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="D27" t="s">
         <v>69</v>
@@ -2354,10 +2309,10 @@
         <v>71</v>
       </c>
       <c r="B28" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C28" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="D28" t="s">
         <v>72</v>
@@ -2373,10 +2328,10 @@
         <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C29" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="D29" t="s">
         <v>75</v>
@@ -2392,10 +2347,10 @@
         <v>77</v>
       </c>
       <c r="B30" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C30" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
@@ -2411,10 +2366,10 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="C31" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="D31" t="s">
         <v>47</v>
@@ -2423,7 +2378,7 @@
         <v>48</v>
       </c>
       <c r="F31" t="s">
-        <v>585</v>
+        <v>570</v>
       </c>
       <c r="G31"/>
       <c r="H31" t="s">
@@ -2435,10 +2390,10 @@
         <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C32" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="D32" t="s">
         <v>80</v>
@@ -2454,10 +2409,10 @@
         <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C33" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="D33" t="s">
         <v>83</v>
@@ -2473,10 +2428,10 @@
         <v>85</v>
       </c>
       <c r="B34" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C34" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="D34" t="s">
         <v>83</v>
@@ -2492,10 +2447,10 @@
         <v>86</v>
       </c>
       <c r="B35" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C35" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="D35" t="s">
         <v>83</v>
@@ -2511,10 +2466,10 @@
         <v>87</v>
       </c>
       <c r="B36" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C36" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="D36" t="s">
         <v>88</v>
@@ -2530,10 +2485,10 @@
         <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C37" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="D37" t="s">
         <v>91</v>
@@ -2549,10 +2504,10 @@
         <v>93</v>
       </c>
       <c r="B38" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C38" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="D38" t="s">
         <v>94</v>
@@ -2568,10 +2523,10 @@
         <v>96</v>
       </c>
       <c r="B39" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C39" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="D39" t="s">
         <v>97</v>
@@ -2587,10 +2542,10 @@
         <v>99</v>
       </c>
       <c r="B40" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C40" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D40" t="s">
         <v>29</v>
@@ -2606,10 +2561,10 @@
         <v>100</v>
       </c>
       <c r="B41" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C41" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D41" t="s">
         <v>29</v>
@@ -2625,10 +2580,10 @@
         <v>101</v>
       </c>
       <c r="B42" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C42" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D42" t="s">
         <v>29</v>
@@ -2644,10 +2599,10 @@
         <v>102</v>
       </c>
       <c r="B43" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C43" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D43" t="s">
         <v>29</v>
@@ -2663,10 +2618,10 @@
         <v>103</v>
       </c>
       <c r="B44" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C44" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D44" t="s">
         <v>29</v>
@@ -2682,10 +2637,10 @@
         <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C45" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
@@ -2701,10 +2656,10 @@
         <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C46" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="D46" t="s">
         <v>75</v>
@@ -2720,10 +2675,10 @@
         <v>106</v>
       </c>
       <c r="B47" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C47" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="D47" t="s">
         <v>14</v>
@@ -2739,10 +2694,10 @@
         <v>107</v>
       </c>
       <c r="B48" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="C48" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="D48" t="s">
         <v>108</v>
@@ -2758,10 +2713,10 @@
         <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C49" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="D49" t="s">
         <v>111</v>
@@ -2777,10 +2732,10 @@
         <v>113</v>
       </c>
       <c r="B50" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C50" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="D50" t="s">
         <v>114</v>
@@ -2796,10 +2751,10 @@
         <v>116</v>
       </c>
       <c r="B51" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C51" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="D51" t="s">
         <v>117</v>
@@ -2815,10 +2770,10 @@
         <v>119</v>
       </c>
       <c r="B52" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C52" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="D52" t="s">
         <v>120</v>
@@ -2834,10 +2789,10 @@
         <v>122</v>
       </c>
       <c r="B53" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C53" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="D53" t="s">
         <v>123</v>
@@ -2853,10 +2808,10 @@
         <v>125</v>
       </c>
       <c r="B54" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C54" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="D54" t="s">
         <v>126</v>
@@ -2872,10 +2827,10 @@
         <v>128</v>
       </c>
       <c r="B55" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C55" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="D55" t="s">
         <v>129</v>
@@ -2891,10 +2846,10 @@
         <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C56" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="D56" t="s">
         <v>132</v>
@@ -2910,10 +2865,10 @@
         <v>134</v>
       </c>
       <c r="B57" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C57" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="D57" t="s">
         <v>135</v>
@@ -2929,10 +2884,10 @@
         <v>137</v>
       </c>
       <c r="B58" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C58" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="D58" t="s">
         <v>117</v>
@@ -2948,10 +2903,10 @@
         <v>138</v>
       </c>
       <c r="B59" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C59" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="D59" t="s">
         <v>139</v>
@@ -2967,10 +2922,10 @@
         <v>141</v>
       </c>
       <c r="B60" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C60" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="D60" t="s">
         <v>142</v>
@@ -2986,10 +2941,10 @@
         <v>144</v>
       </c>
       <c r="B61" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C61" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="D61" t="s">
         <v>142</v>
@@ -3005,10 +2960,10 @@
         <v>145</v>
       </c>
       <c r="B62" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C62" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="D62" t="s">
         <v>142</v>
@@ -3024,10 +2979,10 @@
         <v>146</v>
       </c>
       <c r="B63" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C63" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="D63" t="s">
         <v>147</v>
@@ -3043,10 +2998,10 @@
         <v>149</v>
       </c>
       <c r="B64" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C64" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="D64" t="s">
         <v>150</v>
@@ -3062,10 +3017,10 @@
         <v>152</v>
       </c>
       <c r="B65" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C65" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="D65" t="s">
         <v>150</v>
@@ -3081,10 +3036,10 @@
         <v>153</v>
       </c>
       <c r="B66" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C66" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="D66" t="s">
         <v>150</v>
@@ -3100,10 +3055,10 @@
         <v>154</v>
       </c>
       <c r="B67" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C67" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="D67" t="s">
         <v>120</v>
@@ -3119,10 +3074,10 @@
         <v>155</v>
       </c>
       <c r="B68" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C68" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="D68" t="s">
         <v>14</v>
@@ -3138,10 +3093,10 @@
         <v>156</v>
       </c>
       <c r="B69" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C69" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="D69" t="s">
         <v>14</v>
@@ -3157,10 +3112,10 @@
         <v>157</v>
       </c>
       <c r="B70" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C70" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="D70" t="s">
         <v>158</v>
@@ -3176,10 +3131,10 @@
         <v>160</v>
       </c>
       <c r="B71" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C71" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="D71" t="s">
         <v>161</v>
@@ -3195,10 +3150,10 @@
         <v>163</v>
       </c>
       <c r="B72" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C72" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="D72" t="s">
         <v>158</v>
@@ -3214,10 +3169,10 @@
         <v>164</v>
       </c>
       <c r="B73" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C73" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="D73" t="s">
         <v>165</v>
@@ -3233,10 +3188,10 @@
         <v>167</v>
       </c>
       <c r="B74" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C74" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="D74" t="s">
         <v>168</v>
@@ -3252,10 +3207,10 @@
         <v>170</v>
       </c>
       <c r="B75" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C75" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="D75" t="s">
         <v>168</v>
@@ -3271,10 +3226,10 @@
         <v>171</v>
       </c>
       <c r="B76" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C76" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="D76" t="s">
         <v>158</v>
@@ -3290,10 +3245,10 @@
         <v>172</v>
       </c>
       <c r="B77" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C77" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="D77" t="s">
         <v>168</v>
@@ -3309,10 +3264,10 @@
         <v>173</v>
       </c>
       <c r="B78" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C78" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="D78" t="s">
         <v>158</v>
@@ -3328,10 +3283,10 @@
         <v>174</v>
       </c>
       <c r="B79" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C79" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="D79" t="s">
         <v>168</v>
@@ -3347,10 +3302,10 @@
         <v>175</v>
       </c>
       <c r="B80" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C80" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="D80" t="s">
         <v>176</v>
@@ -3366,10 +3321,10 @@
         <v>178</v>
       </c>
       <c r="B81" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C81" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="D81" t="s">
         <v>176</v>
@@ -3385,10 +3340,10 @@
         <v>179</v>
       </c>
       <c r="B82" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C82" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="D82" t="s">
         <v>176</v>
@@ -3404,10 +3359,10 @@
         <v>180</v>
       </c>
       <c r="B83" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C83" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="D83" t="s">
         <v>158</v>
@@ -3423,10 +3378,10 @@
         <v>181</v>
       </c>
       <c r="B84" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C84" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="D84" t="s">
         <v>168</v>
@@ -3442,10 +3397,10 @@
         <v>182</v>
       </c>
       <c r="B85" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C85" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="D85" t="s">
         <v>168</v>
@@ -3461,10 +3416,10 @@
         <v>183</v>
       </c>
       <c r="B86" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C86" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="D86" t="s">
         <v>184</v>
@@ -3480,10 +3435,10 @@
         <v>186</v>
       </c>
       <c r="B87" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C87" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="D87" t="s">
         <v>187</v>
@@ -3499,10 +3454,10 @@
         <v>189</v>
       </c>
       <c r="B88" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C88" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="D88" t="s">
         <v>187</v>
@@ -3518,10 +3473,10 @@
         <v>190</v>
       </c>
       <c r="B89" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C89" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="D89" t="s">
         <v>187</v>
@@ -3537,10 +3492,10 @@
         <v>191</v>
       </c>
       <c r="B90" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C90" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="D90" t="s">
         <v>161</v>
@@ -3556,10 +3511,10 @@
         <v>192</v>
       </c>
       <c r="B91" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C91" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="D91" t="s">
         <v>193</v>
@@ -3575,10 +3530,10 @@
         <v>195</v>
       </c>
       <c r="B92" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C92" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="D92" t="s">
         <v>114</v>
@@ -3594,10 +3549,10 @@
         <v>196</v>
       </c>
       <c r="B93" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C93" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="D93" t="s">
         <v>114</v>
@@ -3613,10 +3568,10 @@
         <v>197</v>
       </c>
       <c r="B94" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C94" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="D94" t="s">
         <v>198</v>
@@ -3632,10 +3587,10 @@
         <v>200</v>
       </c>
       <c r="B95" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C95" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="D95" t="s">
         <v>139</v>
@@ -3651,10 +3606,10 @@
         <v>201</v>
       </c>
       <c r="B96" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C96" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="D96" t="s">
         <v>202</v>
@@ -3670,10 +3625,10 @@
         <v>204</v>
       </c>
       <c r="B97" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C97" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="D97" t="s">
         <v>202</v>
@@ -3689,10 +3644,10 @@
         <v>205</v>
       </c>
       <c r="B98" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C98" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="D98" t="s">
         <v>206</v>
@@ -3708,10 +3663,10 @@
         <v>208</v>
       </c>
       <c r="B99" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C99" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="D99" t="s">
         <v>209</v>
@@ -3727,10 +3682,10 @@
         <v>211</v>
       </c>
       <c r="B100" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C100" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="D100" t="s">
         <v>212</v>
@@ -3746,10 +3701,10 @@
         <v>214</v>
       </c>
       <c r="B101" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C101" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="D101" t="s">
         <v>215</v>
@@ -3765,10 +3720,10 @@
         <v>217</v>
       </c>
       <c r="B102" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C102" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="D102" t="s">
         <v>218</v>
@@ -3784,10 +3739,10 @@
         <v>220</v>
       </c>
       <c r="B103" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C103" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="D103" t="s">
         <v>221</v>
@@ -3803,10 +3758,10 @@
         <v>223</v>
       </c>
       <c r="B104" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C104" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="D104" t="s">
         <v>221</v>
@@ -3822,10 +3777,10 @@
         <v>224</v>
       </c>
       <c r="B105" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C105" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="D105" t="s">
         <v>225</v>
@@ -3841,10 +3796,10 @@
         <v>227</v>
       </c>
       <c r="B106" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C106" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="D106" t="s">
         <v>225</v>
@@ -3860,10 +3815,10 @@
         <v>228</v>
       </c>
       <c r="B107" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C107" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="D107" t="s">
         <v>225</v>
@@ -3879,10 +3834,10 @@
         <v>229</v>
       </c>
       <c r="B108" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C108" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="D108" t="s">
         <v>225</v>
@@ -3898,10 +3853,10 @@
         <v>230</v>
       </c>
       <c r="B109" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C109" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="D109" t="s">
         <v>20</v>
@@ -3917,10 +3872,10 @@
         <v>231</v>
       </c>
       <c r="B110" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C110" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="D110" t="s">
         <v>232</v>
@@ -3936,10 +3891,10 @@
         <v>234</v>
       </c>
       <c r="B111" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C111" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="D111" t="s">
         <v>235</v>
@@ -3955,10 +3910,10 @@
         <v>237</v>
       </c>
       <c r="B112" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C112" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="D112" t="s">
         <v>235</v>
@@ -3974,10 +3929,10 @@
         <v>238</v>
       </c>
       <c r="B113" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C113" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="D113" t="s">
         <v>235</v>
@@ -3993,10 +3948,10 @@
         <v>239</v>
       </c>
       <c r="B114" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C114" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="D114" t="s">
         <v>235</v>
@@ -4012,10 +3967,10 @@
         <v>240</v>
       </c>
       <c r="B115" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C115" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="D115" t="s">
         <v>241</v>
@@ -4031,10 +3986,10 @@
         <v>243</v>
       </c>
       <c r="B116" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C116" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="D116" t="s">
         <v>241</v>
@@ -4050,10 +4005,10 @@
         <v>244</v>
       </c>
       <c r="B117" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="C117" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="D117" t="s">
         <v>245</v>
@@ -4069,10 +4024,10 @@
         <v>247</v>
       </c>
       <c r="B118" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C118" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="D118" t="s">
         <v>248</v>
@@ -4088,10 +4043,10 @@
         <v>250</v>
       </c>
       <c r="B119" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C119" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="D119" t="s">
         <v>248</v>
@@ -4107,10 +4062,10 @@
         <v>251</v>
       </c>
       <c r="B120" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C120" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="D120" t="s">
         <v>248</v>
@@ -4126,10 +4081,10 @@
         <v>252</v>
       </c>
       <c r="B121" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C121" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="D121" t="s">
         <v>253</v>
@@ -4145,10 +4100,10 @@
         <v>255</v>
       </c>
       <c r="B122" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C122" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="D122" t="s">
         <v>253</v>
@@ -4164,10 +4119,10 @@
         <v>256</v>
       </c>
       <c r="B123" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C123" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="D123" t="s">
         <v>257</v>
@@ -4183,10 +4138,10 @@
         <v>259</v>
       </c>
       <c r="B124" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C124" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="D124" t="s">
         <v>257</v>
@@ -4202,10 +4157,10 @@
         <v>260</v>
       </c>
       <c r="B125" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C125" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="D125" t="s">
         <v>257</v>
@@ -4221,10 +4176,10 @@
         <v>261</v>
       </c>
       <c r="B126" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C126" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="D126" t="s">
         <v>248</v>
@@ -4240,10 +4195,10 @@
         <v>262</v>
       </c>
       <c r="B127" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C127" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="D127" t="s">
         <v>263</v>
@@ -4259,10 +4214,10 @@
         <v>265</v>
       </c>
       <c r="B128" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C128" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="D128" t="s">
         <v>158</v>
@@ -4278,10 +4233,10 @@
         <v>266</v>
       </c>
       <c r="B129" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C129" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D129" t="s">
         <v>29</v>
@@ -4297,10 +4252,10 @@
         <v>267</v>
       </c>
       <c r="B130" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C130" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="D130" t="s">
         <v>120</v>
@@ -4316,10 +4271,10 @@
         <v>268</v>
       </c>
       <c r="B131" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="C131" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="D131" t="s">
         <v>269</v>
@@ -4328,7 +4283,7 @@
         <v>270</v>
       </c>
       <c r="F131" t="s">
-        <v>586</v>
+        <v>571</v>
       </c>
       <c r="G131" t="s">
         <v>271</v>
@@ -4342,10 +4297,10 @@
         <v>273</v>
       </c>
       <c r="B132" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C132" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="D132" t="s">
         <v>35</v>
@@ -4361,10 +4316,10 @@
         <v>274</v>
       </c>
       <c r="B133" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C133" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="D133" t="s">
         <v>275</v>
@@ -4380,10 +4335,10 @@
         <v>277</v>
       </c>
       <c r="B134" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C134" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="D134" t="s">
         <v>278</v>
@@ -4399,10 +4354,10 @@
         <v>280</v>
       </c>
       <c r="B135" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C135" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="D135" t="s">
         <v>281</v>
@@ -4418,10 +4373,10 @@
         <v>283</v>
       </c>
       <c r="B136" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C136" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="D136" t="s">
         <v>281</v>
@@ -4437,10 +4392,10 @@
         <v>285</v>
       </c>
       <c r="B137" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C137" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="D137" t="s">
         <v>281</v>
@@ -4456,10 +4411,10 @@
         <v>287</v>
       </c>
       <c r="B138" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C138" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="D138" t="s">
         <v>221</v>
@@ -4475,10 +4430,10 @@
         <v>288</v>
       </c>
       <c r="B139" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C139" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="D139" t="s">
         <v>289</v>
@@ -4494,10 +4449,10 @@
         <v>291</v>
       </c>
       <c r="B140" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C140" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="D140" t="s">
         <v>120</v>
@@ -4513,10 +4468,10 @@
         <v>292</v>
       </c>
       <c r="B141" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C141" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="D141" t="s">
         <v>123</v>
@@ -4532,10 +4487,10 @@
         <v>293</v>
       </c>
       <c r="B142" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C142" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="D142" t="s">
         <v>117</v>
@@ -4551,10 +4506,10 @@
         <v>294</v>
       </c>
       <c r="B143" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C143" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="D143" t="s">
         <v>35</v>
@@ -4570,10 +4525,10 @@
         <v>295</v>
       </c>
       <c r="B144" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C144" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="D144" t="s">
         <v>38</v>
@@ -4589,10 +4544,10 @@
         <v>296</v>
       </c>
       <c r="B145" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="C145" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="D145" t="s">
         <v>117</v>
@@ -4608,10 +4563,10 @@
         <v>297</v>
       </c>
       <c r="B146" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="C146" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="D146" t="s">
         <v>35</v>
@@ -4627,10 +4582,10 @@
         <v>298</v>
       </c>
       <c r="B147" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C147" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="D147" t="s">
         <v>299</v>
@@ -4646,10 +4601,10 @@
         <v>301</v>
       </c>
       <c r="B148" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C148" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="D148" t="s">
         <v>302</v>
@@ -4665,10 +4620,10 @@
         <v>304</v>
       </c>
       <c r="B149" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C149" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="D149" t="s">
         <v>302</v>
@@ -4684,10 +4639,10 @@
         <v>305</v>
       </c>
       <c r="B150" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C150" t="s">
-        <v>551</v>
+        <v>538</v>
       </c>
       <c r="D150" t="s">
         <v>306</v>
@@ -4703,10 +4658,10 @@
         <v>308</v>
       </c>
       <c r="B151" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="C151" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="D151" t="s">
         <v>150</v>
@@ -4722,10 +4677,10 @@
         <v>309</v>
       </c>
       <c r="B152" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="C152" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="D152" t="s">
         <v>310</v>
@@ -4741,10 +4696,10 @@
         <v>312</v>
       </c>
       <c r="B153" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="C153" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="D153" t="s">
         <v>313</v>
@@ -4760,10 +4715,10 @@
         <v>315</v>
       </c>
       <c r="B154" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="C154" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="D154" t="s">
         <v>316</v>
@@ -4779,10 +4734,10 @@
         <v>318</v>
       </c>
       <c r="B155" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="C155" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="D155" t="s">
         <v>316</v>
@@ -4798,10 +4753,10 @@
         <v>319</v>
       </c>
       <c r="B156" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C156" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="D156" t="s">
         <v>75</v>
@@ -4817,10 +4772,10 @@
         <v>320</v>
       </c>
       <c r="B157" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="C157" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="D157" t="s">
         <v>111</v>
@@ -4836,10 +4791,10 @@
         <v>321</v>
       </c>
       <c r="B158" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C158" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="D158" t="s">
         <v>221</v>
@@ -4855,10 +4810,10 @@
         <v>322</v>
       </c>
       <c r="B159" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="C159" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="D159" t="s">
         <v>150</v>
@@ -4874,10 +4829,10 @@
         <v>323</v>
       </c>
       <c r="B160" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="C160" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="D160" t="s">
         <v>150</v>
@@ -4893,10 +4848,10 @@
         <v>324</v>
       </c>
       <c r="B161" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="C161" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="D161" t="s">
         <v>150</v>
@@ -4912,10 +4867,10 @@
         <v>325</v>
       </c>
       <c r="B162" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="C162" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="D162" t="s">
         <v>108</v>
@@ -4931,10 +4886,10 @@
         <v>326</v>
       </c>
       <c r="B163" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C163" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="D163" t="s">
         <v>327</v>
@@ -4950,10 +4905,10 @@
         <v>329</v>
       </c>
       <c r="B164" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C164" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="D164" t="s">
         <v>289</v>
@@ -4969,10 +4924,10 @@
         <v>330</v>
       </c>
       <c r="B165" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C165" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="D165" t="s">
         <v>331</v>
@@ -4988,7 +4943,7 @@
         <v>333</v>
       </c>
       <c r="B166" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="C166" t="s">
         <v>335</v>
@@ -5007,7 +4962,7 @@
         <v>336</v>
       </c>
       <c r="B167" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="C167" t="s">
         <v>335</v>
@@ -5026,10 +4981,10 @@
         <v>337</v>
       </c>
       <c r="B168" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C168" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="D168" t="s">
         <v>338</v>
@@ -5045,10 +5000,10 @@
         <v>340</v>
       </c>
       <c r="B169" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="C169" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="D169" t="s">
         <v>341</v>
@@ -5064,10 +5019,10 @@
         <v>343</v>
       </c>
       <c r="B170" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="C170" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="D170" t="s">
         <v>344</v>
@@ -5083,10 +5038,10 @@
         <v>346</v>
       </c>
       <c r="B171" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="C171" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="D171" t="s">
         <v>347</v>
@@ -5102,10 +5057,10 @@
         <v>349</v>
       </c>
       <c r="B172" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="C172" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="D172" t="s">
         <v>139</v>
@@ -5121,10 +5076,10 @@
         <v>350</v>
       </c>
       <c r="B173" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="C173" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="D173" t="s">
         <v>139</v>
@@ -5140,10 +5095,10 @@
         <v>351</v>
       </c>
       <c r="B174" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="C174" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="D174" t="s">
         <v>352</v>
@@ -5159,10 +5114,10 @@
         <v>354</v>
       </c>
       <c r="B175" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="C175" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="D175" t="s">
         <v>355</v>
@@ -5178,10 +5133,10 @@
         <v>357</v>
       </c>
       <c r="B176" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="C176" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="D176" t="s">
         <v>355</v>
@@ -5197,10 +5152,10 @@
         <v>358</v>
       </c>
       <c r="B177" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="C177" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="D177" t="s">
         <v>359</v>
@@ -5216,10 +5171,10 @@
         <v>361</v>
       </c>
       <c r="B178" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="C178" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D178" t="s">
         <v>29</v>
@@ -5235,10 +5190,10 @@
         <v>362</v>
       </c>
       <c r="B179" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="C179" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D179" t="s">
         <v>29</v>
@@ -5254,10 +5209,10 @@
         <v>363</v>
       </c>
       <c r="B180" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="C180" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D180" t="s">
         <v>29</v>
@@ -5273,10 +5228,10 @@
         <v>364</v>
       </c>
       <c r="B181" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="C181" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D181" t="s">
         <v>29</v>
@@ -5292,10 +5247,10 @@
         <v>365</v>
       </c>
       <c r="B182" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="C182" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D182" t="s">
         <v>29</v>
@@ -5311,10 +5266,10 @@
         <v>366</v>
       </c>
       <c r="B183" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="C183" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D183" t="s">
         <v>29</v>
@@ -5330,10 +5285,10 @@
         <v>367</v>
       </c>
       <c r="B184" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="C184" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D184" t="s">
         <v>29</v>
@@ -5349,10 +5304,10 @@
         <v>368</v>
       </c>
       <c r="B185" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="C185" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D185" t="s">
         <v>29</v>
@@ -5368,10 +5323,10 @@
         <v>369</v>
       </c>
       <c r="B186" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="C186" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D186" t="s">
         <v>29</v>
@@ -5387,10 +5342,10 @@
         <v>370</v>
       </c>
       <c r="B187" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="C187" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D187" t="s">
         <v>29</v>
@@ -5406,10 +5361,10 @@
         <v>371</v>
       </c>
       <c r="B188" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="C188" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="D188" t="s">
         <v>14</v>
@@ -5425,10 +5380,10 @@
         <v>372</v>
       </c>
       <c r="B189" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="C189" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="D189" t="s">
         <v>373</v>
@@ -5444,10 +5399,10 @@
         <v>375</v>
       </c>
       <c r="B190" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="C190" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="D190" t="s">
         <v>376</v>
@@ -5463,10 +5418,10 @@
         <v>378</v>
       </c>
       <c r="B191" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="C191" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="D191" t="s">
         <v>376</v>
@@ -5482,10 +5437,10 @@
         <v>379</v>
       </c>
       <c r="B192" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="C192" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="D192" t="s">
         <v>380</v>
@@ -5501,10 +5456,10 @@
         <v>382</v>
       </c>
       <c r="B193" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="C193" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="D193" t="s">
         <v>383</v>
@@ -5520,10 +5475,10 @@
         <v>385</v>
       </c>
       <c r="B194" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="C194" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="D194" t="s">
         <v>386</v>
@@ -5539,10 +5494,10 @@
         <v>388</v>
       </c>
       <c r="B195" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="C195" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="D195" t="s">
         <v>389</v>
@@ -5558,10 +5513,10 @@
         <v>391</v>
       </c>
       <c r="B196" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="C196" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D196" t="s">
         <v>392</v>
@@ -5577,10 +5532,10 @@
         <v>394</v>
       </c>
       <c r="B197" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="C197" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="D197" t="s">
         <v>395</v>
@@ -5596,10 +5551,10 @@
         <v>397</v>
       </c>
       <c r="B198" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="C198" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="D198" t="s">
         <v>398</v>
@@ -5615,10 +5570,10 @@
         <v>400</v>
       </c>
       <c r="B199" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="C199" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="D199" t="s">
         <v>401</v>
@@ -5634,10 +5589,10 @@
         <v>403</v>
       </c>
       <c r="B200" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="C200" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="D200" t="s">
         <v>404</v>
@@ -5653,10 +5608,10 @@
         <v>406</v>
       </c>
       <c r="B201" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="C201" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="D201" t="s">
         <v>407</v>
@@ -5672,10 +5627,10 @@
         <v>409</v>
       </c>
       <c r="B202" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="C202" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="D202" t="s">
         <v>410</v>
@@ -5691,10 +5646,10 @@
         <v>412</v>
       </c>
       <c r="B203" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="C203" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="D203" t="s">
         <v>413</v>
@@ -5710,10 +5665,10 @@
         <v>415</v>
       </c>
       <c r="B204" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="C204" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="D204" t="s">
         <v>59</v>
@@ -5729,10 +5684,10 @@
         <v>416</v>
       </c>
       <c r="B205" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="C205" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="D205" t="s">
         <v>417</v>
@@ -5748,10 +5703,10 @@
         <v>419</v>
       </c>
       <c r="B206" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="C206" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="D206" t="s">
         <v>417</v>
@@ -5767,10 +5722,10 @@
         <v>420</v>
       </c>
       <c r="B207" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="C207" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="D207" t="s">
         <v>421</v>
@@ -5786,10 +5741,10 @@
         <v>423</v>
       </c>
       <c r="B208" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="C208" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="D208" t="s">
         <v>424</v>
@@ -5805,10 +5760,10 @@
         <v>426</v>
       </c>
       <c r="B209" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="C209" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="D209" t="s">
         <v>427</v>
@@ -5818,139 +5773,6 @@
       </c>
       <c r="G209"/>
       <c r="H209"/>
-    </row>
-    <row r="210">
-      <c r="A210" t="s">
-        <v>429</v>
-      </c>
-      <c r="B210" t="s">
-        <v>476</v>
-      </c>
-      <c r="C210" t="s">
-        <v>582</v>
-      </c>
-      <c r="D210" t="s">
-        <v>427</v>
-      </c>
-      <c r="E210" t="s">
-        <v>428</v>
-      </c>
-      <c r="G210"/>
-      <c r="H210"/>
-    </row>
-    <row r="211">
-      <c r="A211" t="s">
-        <v>430</v>
-      </c>
-      <c r="B211" t="s">
-        <v>477</v>
-      </c>
-      <c r="C211" t="s">
-        <v>583</v>
-      </c>
-      <c r="D211" t="s">
-        <v>431</v>
-      </c>
-      <c r="E211" t="s">
-        <v>432</v>
-      </c>
-      <c r="G211"/>
-      <c r="H211"/>
-    </row>
-    <row r="212">
-      <c r="A212" t="s">
-        <v>433</v>
-      </c>
-      <c r="B212" t="s">
-        <v>477</v>
-      </c>
-      <c r="C212" t="s">
-        <v>583</v>
-      </c>
-      <c r="D212" t="s">
-        <v>431</v>
-      </c>
-      <c r="E212" t="s">
-        <v>432</v>
-      </c>
-      <c r="G212"/>
-      <c r="H212"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="s">
-        <v>434</v>
-      </c>
-      <c r="B213" t="s">
-        <v>477</v>
-      </c>
-      <c r="C213" t="s">
-        <v>583</v>
-      </c>
-      <c r="D213" t="s">
-        <v>431</v>
-      </c>
-      <c r="E213" t="s">
-        <v>432</v>
-      </c>
-      <c r="G213"/>
-      <c r="H213"/>
-    </row>
-    <row r="214">
-      <c r="A214" t="s">
-        <v>435</v>
-      </c>
-      <c r="B214" t="s">
-        <v>477</v>
-      </c>
-      <c r="C214" t="s">
-        <v>584</v>
-      </c>
-      <c r="D214" t="s">
-        <v>436</v>
-      </c>
-      <c r="E214" t="s">
-        <v>437</v>
-      </c>
-      <c r="G214"/>
-      <c r="H214"/>
-    </row>
-    <row r="215">
-      <c r="A215" t="s">
-        <v>438</v>
-      </c>
-      <c r="B215" t="s">
-        <v>477</v>
-      </c>
-      <c r="C215" t="s">
-        <v>584</v>
-      </c>
-      <c r="D215" t="s">
-        <v>436</v>
-      </c>
-      <c r="E215" t="s">
-        <v>437</v>
-      </c>
-      <c r="G215"/>
-      <c r="H215"/>
-    </row>
-    <row r="216">
-      <c r="A216" t="s">
-        <v>439</v>
-      </c>
-      <c r="B216" t="s">
-        <v>477</v>
-      </c>
-      <c r="C216" t="s">
-        <v>584</v>
-      </c>
-      <c r="D216" t="s">
-        <v>436</v>
-      </c>
-      <c r="E216" t="s">
-        <v>437</v>
-      </c>
-      <c r="G216"/>
-      <c r="H216"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>
